--- a/光伏配储项目/电价数据/2026/祯州站.xlsx
+++ b/光伏配储项目/电价数据/2026/祯州站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.30881</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.4962</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5906399999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.14233</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45916</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42607</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50125</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12304</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13527</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07429999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11405</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.57585</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.21878</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05084</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.77455</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.20786</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21953</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22944</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23461</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21866</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6875399999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14919</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.55813</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.70245</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7928200000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.7267899999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7309500000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.36263</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65816</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.11329</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.72112</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.4497</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.30275</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.53013</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.68913</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.9325399999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.35612</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87166</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7964600000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75701</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51728</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42537</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70841</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77162</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87148</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91626</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51467</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5027699999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48505</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.87634</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7200599999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.81562</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45616</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50866</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50613</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7770900000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9910099999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52061</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.88598</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8427899999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49543</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7242799999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.32051</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07312</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.02096</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46887</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5451</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49788</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5211699999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.92836</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6204500000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.97515</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.4033</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.60445</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17422</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.16044</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.6506</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.55284</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.70829</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.48632</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.53772</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.09474</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.43016</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90216</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.52289</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.63618</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.41941</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7867999999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80803</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44895</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50764</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48677</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48692</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44302</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47205</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44387</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.52766</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.73752</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.9665900000000001</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.86686</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.80916</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55404</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49563</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8160499999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59089</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7222499999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8109500000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52607</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.55216</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79745</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.28476</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6840900000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.59693</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49334</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.8191000000000001</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52351</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5036499999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57009</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59535</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5424600000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5622699999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26432</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61621</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.88803</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.53869</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.58084</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.02395</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.09885</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.38863</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.93188</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.88464</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.7097899999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.98994</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61012</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.94169</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56252</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.38653</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.90304</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55928</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48181</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61549</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.5222599999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45665</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34195</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5209900000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.53944</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.81024</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.68267</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.95363</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.33417</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.8690599999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.02771</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.56418</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.75787</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.53443</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.37387</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.28478</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.14014</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.66909</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1.05533</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60458</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.04496</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>1.04659</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.91189</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.50827</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.60691</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49518</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45029</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46168</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47405</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51967</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.10052</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.00465</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.5902</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.07624</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.95153</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50095</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.8682300000000001</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.81368</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.68801</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.57845</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31735</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7549</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.8938200000000001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.45139</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19712</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.21864</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15187</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28472</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.16065</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.19047</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.25023</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.23164</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05146</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.20901</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06377000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.05207</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>7.000000000000001e-05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.06679</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46144</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48668</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34445</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.5914199999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10275</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2151</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05368999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20266</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06558</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.14653</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06924</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06748</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33163</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78523</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8757200000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.03065</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.67933</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39989</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5601799999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5849800000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7093400000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8766799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46651</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5535800000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.81997</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5730700000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85303</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87499</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.63217</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6332000000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.76975</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34774</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91416</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39123</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46414</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19778</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25377</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44063</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5373600000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8675700000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44246</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13988</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68711</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77744</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63883</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.51006</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40391</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49061</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4308999999999999</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40556</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46503</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42642</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48707</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5257500000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15466</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25994</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.54427</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.79038</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44117</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3084</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24853</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24267</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26464</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22911</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.22141</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.28529</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.21688</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.24222</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.26368</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.21897</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33552</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.89212</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.93649</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23964</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.5517300000000001</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.57933</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.63221</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5698</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.9248099999999999</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.99425</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.95169</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.21784</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.8274900000000001</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.25693</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.61856</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.77222</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.49893</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.43312</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34949</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47637</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.64079</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.74571</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.72982</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.54983</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.66088</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.43826</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.11241</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.7428400000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.72641</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.07679</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.69685</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.27463</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.14617</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.18219</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.64716</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.00629</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.18753</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6244299999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.56924</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.28243</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.55411</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.72708</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.5799</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.7395</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.30454</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.6275</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.10701</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.8227599999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.45941</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.8305900000000001</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.7972400000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.88575</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.81275</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.39828</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.9346</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.9145599999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.89647</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.17127</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.8436399999999999</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.66496</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.61563</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24123</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31281</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.14869</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5155599999999999</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.9295399999999999</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.31533</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.55658</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.2191</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.55061</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.96147</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.96012</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34359</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7831</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.39508</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42863</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.56584</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.51069</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.61022</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.46222</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.52319</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.65671</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65111</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.74436</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.64638</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.9467300000000001</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.7492000000000001</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3349</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40505</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.60062</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.49948</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.9450700000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.6189600000000001</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.03171</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.49708</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.73217</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.09396</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.75627</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.81272</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.60612</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.99352</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.84323</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48004</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.78252</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7605599999999999</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.05912</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.79038</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.05242</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.56076</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.52482</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.55655</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.0924</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.0502</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.52375</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.9689</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.1416</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9825499999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9369</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.84822</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.60996</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.52629</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.80833</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47706</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6214700000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5070899999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46201</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.60997</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.40002</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.0362</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.44726</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.48389</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.5636</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6572100000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.70568</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.02823</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46023</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47453</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.47475</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50817</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6271599999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73658</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8266699999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.59436</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7177</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.62521</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50243</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7385</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7654</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61819</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66653</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44198</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43958</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50836</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46563</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15193</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21693</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46224</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.26288</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.25322</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24468</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27358</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25774</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10014</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25696</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03487</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19349</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24851</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24012</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27607</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32532</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.24521</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.24473</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.24734</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.24733</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.24403</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.24403</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.24601</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.2408</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.24403</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.24435</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.24488</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.24467</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25175</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16781</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26738</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21494</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01303</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00017</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14598</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01536</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04287</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04076</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02925</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03816</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01882</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03613</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20162</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24878</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33279</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7410099999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6382899999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25084</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24082</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24646</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26759</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43719</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.68788</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.84433</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8777</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85199</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20861</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26511</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04024</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25721</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.26954</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.01743</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00757</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05372</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25199</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4714</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.48274</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.78234</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.7253999999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.75059</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.32292</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.95894</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.75337</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.82525</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.79573</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8404700000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8386699999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84297</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94017</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.75614</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.7916799999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7591100000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36427</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61295</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.66423</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5746100000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49391</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47647</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.47546</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42672</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44219</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25326</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.61626</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.5209600000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.45202</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33166</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.74121</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.49817</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.43996</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45775</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.81399</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.13508</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48505</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.57708</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5669500000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.05889</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.87466</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.54586</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.66753</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.51276</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.44212</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.48602</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23042</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34761</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43487</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50848</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.61084</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.26887</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.0436</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.68369</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.90659</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.66365</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.60556</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.83526</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.77462</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.99863</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89673</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.81536</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7578400000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35203</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.19528</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.47558</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.7904500000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21535</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.57711</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.79369</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.49048</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.41421</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.41167</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.50234</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.68625</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.53132</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.48817</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.66355</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47842</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.50373</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35843</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9531499999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.47716</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5057699999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43099</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.48209</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.50917</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5089399999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5855499999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.48526</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45317</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35585</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17569</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19809</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14237</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04509000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12104</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22531</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26363</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14926</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14382</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19398</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22624</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15257</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15348</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19643</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14195</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.49753</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.55467</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46546</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38215</v>
       </c>
     </row>
   </sheetData>
